--- a/data/trans_orig/Q5409A_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5409A_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si necesita sonda u otros dispositivos y es capaz de utilizarlos en 2023</t>
+          <t>Población según si necesita sonda u otros dispositivos y es capaz de utilizarlos en 2023 (tasa de respuesta: 96,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>318</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>706</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6071</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10702</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12377</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18506</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19632</t>
+          <t>19403</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27949</t>
+          <t>27863</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,97%</t>
         </is>
       </c>
     </row>
@@ -956,97 +956,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>912</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3490</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>14,1%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3465</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>2981</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>468</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>7710</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10083</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>333</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3590</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>501</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>12488</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>20067</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17431</t>
+          <t>17843</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26901</t>
+          <t>27267</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>432</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>494</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6911</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9827</t>
+          <t>9762</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>5977</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14541</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5574</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13290</t>
+          <t>13186</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2456</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7112</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13617</t>
+          <t>13514</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13474</t>
+          <t>13287</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20414</t>
+          <t>20536</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22978</t>
+          <t>23177</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32556</t>
+          <t>32406</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,16%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,62 +2355,62 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>2922</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>2734</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>541</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>531</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>540</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11819</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12611</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23386</t>
+          <t>23198</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33911</t>
+          <t>33688</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31731</t>
+          <t>31276</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>44039</t>
+          <t>44664</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>61,25%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>397</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>389</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9773</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11950</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14813</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16630</t>
+          <t>16537</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>16642</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>29032</t>
+          <t>29051</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,84%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>8726</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18939</t>
+          <t>18600</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10710</t>
+          <t>10740</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>21715</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28647</t>
+          <t>28398</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41147</t>
+          <t>40889</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>69736</t>
+          <t>69702</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>85081</t>
+          <t>86273</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>101471</t>
+          <t>101977</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>122527</t>
+          <t>122535</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8716</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11120</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24567</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>19184</t>
+          <t>18575</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>32819</t>
+          <t>32645</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16704</t>
+          <t>16957</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>29221</t>
+          <t>29017</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13490</t>
+          <t>13822</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25376</t>
+          <t>25030</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>33865</t>
+          <t>34189</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>50963</t>
+          <t>51090</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5409A_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5409A_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>339</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>753</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8625</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>6569</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10702</t>
+          <t>11502</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15383</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12211</t>
+          <t>12585</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18558</t>
+          <t>19607</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>24008</t>
+          <t>25473</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19403</t>
+          <t>20739</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27863</t>
+          <t>29673</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,75%</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>677</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>677</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10222</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>338</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,22 +1212,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6699</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12926</t>
+          <t>13675</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12926</t>
+          <t>13675</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12926</t>
+          <t>13675</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24744</t>
+          <t>26559</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24744</t>
+          <t>26559</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24744</t>
+          <t>26559</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>37670</t>
+          <t>40234</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>37670</t>
+          <t>40234</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37670</t>
+          <t>40234</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>477</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1591</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>9692</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12488</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20067</t>
+          <t>22062</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>22296</t>
+          <t>24162</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>18883</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27267</t>
+          <t>29359</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>57,29%</t>
         </is>
       </c>
     </row>
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,17 +1703,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>574</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1698</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9762</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>11267</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>7096</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>16315</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>9394</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13186</t>
+          <t>14988</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15648</t>
+          <t>16886</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15648</t>
+          <t>16886</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15648</t>
+          <t>16886</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30753</t>
+          <t>34358</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30753</t>
+          <t>34358</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30753</t>
+          <t>34358</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>46401</t>
+          <t>51245</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>46401</t>
+          <t>51245</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>46401</t>
+          <t>51245</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2543</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10665</t>
+          <t>11983</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13514</t>
+          <t>15365</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17300</t>
+          <t>19918</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13287</t>
+          <t>15921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20536</t>
+          <t>23644</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>27965</t>
+          <t>31901</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23177</t>
+          <t>26254</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32406</t>
+          <t>37058</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>680</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>680</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>577</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>7974</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16387</t>
+          <t>18744</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16387</t>
+          <t>18744</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16387</t>
+          <t>18744</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25614</t>
+          <t>29240</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25614</t>
+          <t>29240</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25614</t>
+          <t>29240</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>42001</t>
+          <t>47984</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42001</t>
+          <t>47984</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42001</t>
+          <t>47984</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>610</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>28806</t>
+          <t>30545</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23198</t>
+          <t>24664</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33688</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>37820</t>
+          <t>40044</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31276</t>
+          <t>33399</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>44664</t>
+          <t>46962</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>59,46%</t>
         </is>
       </c>
     </row>
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>417</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,22 +3067,22 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>417</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>636</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6860</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9391</t>
+          <t>12538</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>8840</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11452</t>
+          <t>15178</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>11319</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>15099</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>11633</t>
+          <t>12946</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16537</t>
+          <t>18513</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>22667</t>
+          <t>24265</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16642</t>
+          <t>18604</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>29051</t>
+          <t>31172</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,47%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>23408</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>23408</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>23408</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>50870</t>
+          <t>55576</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>50870</t>
+          <t>55576</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>50870</t>
+          <t>55576</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>72921</t>
+          <t>78984</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>72921</t>
+          <t>78984</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>72921</t>
+          <t>78984</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>14386</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8726</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18600</t>
+          <t>21603</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>11729</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>23788</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>34330</t>
+          <t>36958</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28398</t>
+          <t>29712</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>40889</t>
+          <t>44015</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>77759</t>
+          <t>84622</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>69702</t>
+          <t>75774</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>86273</t>
+          <t>93383</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>112089</t>
+          <t>121580</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>101977</t>
+          <t>110388</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>122535</t>
+          <t>133015</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>60,89%</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>680</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>9850</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>12596</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>18412</t>
+          <t>21312</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>15315</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>28951</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>24987</t>
+          <t>28969</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>18575</t>
+          <t>21866</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>32645</t>
+          <t>37961</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -3905,17 +3905,17 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>23029</t>
+          <t>24985</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>18642</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>29017</t>
+          <t>32158</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>18678</t>
+          <t>20794</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>14384</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25030</t>
+          <t>27907</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,17 +3975,17 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>41706</t>
+          <t>45779</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>34189</t>
+          <t>37395</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>51090</t>
+          <t>56238</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>67012</t>
+          <t>72713</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>67012</t>
+          <t>72713</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>67012</t>
+          <t>72713</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>131981</t>
+          <t>145734</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>131981</t>
+          <t>145734</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>131981</t>
+          <t>145734</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>198993</t>
+          <t>218447</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>198993</t>
+          <t>218447</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>198993</t>
+          <t>218447</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
